--- a/rolling_dy_results.xlsx
+++ b/rolling_dy_results.xlsx
@@ -5675,7 +5675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5701,10 +5701,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>F_stat</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>P_value</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Significant</t>
         </is>
@@ -5727,12 +5732,15 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2384660929955905</v>
-      </c>
-      <c r="F2" t="b">
+        <v>0.7228960985401377</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.486055656089793</v>
+      </c>
+      <c r="G2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5753,12 +5761,15 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3017248229221599</v>
-      </c>
-      <c r="F3" t="b">
+        <v>0.5703722282891405</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5658307108492273</v>
+      </c>
+      <c r="G3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5779,12 +5790,15 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2260869841597052</v>
-      </c>
-      <c r="F4" t="b">
+        <v>0.7737692728522719</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4620453020831123</v>
+      </c>
+      <c r="G4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5805,12 +5819,15 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1671253658681015</v>
-      </c>
-      <c r="F5" t="b">
+        <v>0.9592094097941241</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3841838152333341</v>
+      </c>
+      <c r="G5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5831,12 +5848,15 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5623225388206532</v>
-      </c>
-      <c r="F6" t="b">
+        <v>0.2288202366307604</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.7955884196894462</v>
+      </c>
+      <c r="G6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5857,12 +5877,15 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6014574337617816</v>
-      </c>
-      <c r="F7" t="b">
+        <v>0.2176508112996156</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8045132421334489</v>
+      </c>
+      <c r="G7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5883,12 +5906,15 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4310548549135047</v>
-      </c>
-      <c r="F8" t="b">
+        <v>0.9309623207223374</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3951316607340203</v>
+      </c>
+      <c r="G8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5909,12 +5935,15 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2199646643965319</v>
-      </c>
-      <c r="F9" t="b">
+        <v>1.207072124851294</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3002926521862705</v>
+      </c>
+      <c r="G9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5935,12 +5964,15 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2288478827830627</v>
-      </c>
-      <c r="F10" t="b">
+        <v>0.9172749919738425</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4058560531059978</v>
+      </c>
+      <c r="G10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5961,12 +5993,15 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2615422278721986</v>
-      </c>
-      <c r="F11" t="b">
+        <v>0.8606839729432808</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4286980306284555</v>
+      </c>
+      <c r="G11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5987,12 +6022,15 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6636181385274311</v>
-      </c>
-      <c r="F12" t="b">
+        <v>0.6609856420908048</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5205461291801068</v>
+      </c>
+      <c r="G12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6013,12 +6051,15 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9690845390518696</v>
-      </c>
-      <c r="F13" t="b">
+        <v>0.7091825145166164</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4966552983162369</v>
+      </c>
+      <c r="G13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6039,12 +6080,15 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8028471854334858</v>
-      </c>
-      <c r="F14" t="b">
+        <v>0.02008047324085002</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9801272497575571</v>
+      </c>
+      <c r="G14" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6065,12 +6109,15 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7387353737668522</v>
-      </c>
-      <c r="F15" t="b">
+        <v>0.02758239666028365</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9728084786301878</v>
+      </c>
+      <c r="G15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6091,12 +6138,15 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9628585029598573</v>
-      </c>
-      <c r="F16" t="b">
+        <v>0.5365937606614395</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5878794869626418</v>
+      </c>
+      <c r="G16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6117,12 +6167,15 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6449378672972952</v>
-      </c>
-      <c r="F17" t="b">
+        <v>0.8357274550195308</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4391913837526613</v>
+      </c>
+      <c r="G17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6137,7 +6190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6175,7 +6228,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Crypto_Trad_Difference</t>
+          <t>Crypto_Trad_Difference_Absolute</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -6185,91 +6238,161 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Crypto_Trad_T_Stat</t>
+          <t>Crypto_Trad_Difference_Relative_Pct</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.181124603219071</v>
+        <v>-16.55961308770648</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crypto_Trad_P_Value</t>
+          <t>Crypto_Trad_T_Stat</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001592749401567449</v>
+        <v>3.181124603219071</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Crypto_Trad_Cohen_d</t>
+          <t>Crypto_Trad_P_Value</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.3187047546039589</v>
+        <v>0.001592749401567449</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total_Normal_Mean</t>
+          <t>Crypto_Trad_P_Value_Bonferroni_Adjusted</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51.48973297594701</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Total_Bubble_Mean</t>
+          <t>Crypto_Trad_Cohen_d</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47.53695381735326</v>
+        <v>-0.3187047546039589</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Total_Difference</t>
+          <t>Total_Normal_Mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-3.952779158593742</v>
+        <v>51.48973297594701</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Total_T_Stat</t>
+          <t>Total_Bubble_Mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.977825676051739</v>
+        <v>47.53695381735326</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total_P_Value</t>
+          <t>Total_Difference_Absolute</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.006098272340369e-06</v>
+        <v>-3.952779158593742</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Total_Difference_Relative_Pct</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-7.676829787484525</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Total_T_Stat</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4.977825676051739</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Total_P_Value</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.006098272340369e-06</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Total_P_Value_Bonferroni_Adjusted</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Total_Cohen_d</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B17" t="n">
         <v>-0.5055808704209612</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>N_Normal_Windows</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>N_Bubble_Windows</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Bonferroni_Alpha</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.025</v>
       </c>
     </row>
   </sheetData>
